--- a/data/trans_orig/RUIDO_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>46777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164579</t>
+          <t>165190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191395</t>
+          <t>191144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175188</t>
+          <t>175995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205185</t>
+          <t>206168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351033</t>
+          <t>348883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391515</t>
+          <t>392450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>51504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83042</t>
+          <t>82235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83408</t>
+          <t>82473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123890</t>
+          <t>126040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61185</t>
+          <t>60717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57621</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73845</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110171</t>
+          <t>109394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131072</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>48522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69737</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239995</t>
+          <t>240862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273672</t>
+          <t>272843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>520382</t>
+          <t>518404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568736</t>
+          <t>569163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56454</t>
+          <t>57283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>89264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>117636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147539</t>
+          <t>147112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195893</t>
+          <t>197871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26270</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28946</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24143</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26916</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46777</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4248</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8335</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>178552</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>163701</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>190497</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>176881</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>165190</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>191144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>192962</t>
+          <t>150813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175995</t>
+          <t>140668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206168</t>
+          <t>160005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>369842</t>
+          <t>329365</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>348883</t>
+          <t>313136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392450</t>
+          <t>344015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48713</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75509</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39813</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25550</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51504</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82235</t>
+          <t>50575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>101088</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82473</t>
+          <t>86438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126040</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61789</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53570</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68040</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46711</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60717</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66492</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>61117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>120729</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>104626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131386</t>
+          <t>124914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26671</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34890</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30805</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24324</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38330</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,22%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59179</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70514</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,57 +1749,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>255260</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>240862</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>272843</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224185</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>212332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>543554</t>
+          <t>490796</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>518404</t>
+          <t>469980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569163</t>
+          <t>510093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -1862,57 +1862,57 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91354</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75649</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>74866</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57283</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>89264</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>76087</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82705</t>
+          <t>63968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>167441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147112</t>
+          <t>148144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197871</t>
+          <t>188257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>467</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
